--- a/phys5v48hw/hw6/hw6CPUData.xlsx
+++ b/phys5v48hw/hw6/hw6CPUData.xlsx
@@ -1,30 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25200" windowHeight="11985"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
-      <sz val="11.000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -40,28 +44,87 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -107,13 +170,13 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Angsana New"/>
+        <a:font script="Thai" typeface="Tahoma"/>
         <a:font script="Ethi" typeface="Nyala"/>
         <a:font script="Beng" typeface="Vrinda"/>
         <a:font script="Gujr" typeface="Shruti"/>
@@ -141,13 +204,13 @@
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Cordia New"/>
+        <a:font script="Thai" typeface="Tahoma"/>
         <a:font script="Ethi" typeface="Nyala"/>
         <a:font script="Beng" typeface="Vrinda"/>
         <a:font script="Gujr" typeface="Shruti"/>
@@ -344,267 +407,73 @@
 </a:theme>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="New Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="44546A"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="ED7D31"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="FFC000"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="4472C4"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="70AD47"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0563C1"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="954F72"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults/>
-</a:theme>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="1" orientation="portrait" verticalDpi="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>CPU Time (s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>RK2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0.0015572579577565193</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>RK4</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>9.390106424689293e-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Forward Euler</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2.4950015358626842e-05</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/phys5v48hw/hw6/hw6CPUData.xlsx
+++ b/phys5v48hw/hw6/hw6CPUData.xlsx
@@ -439,7 +439,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.0015572579577565193</t>
+          <t>0.002077734097838402</t>
         </is>
       </c>
     </row>
@@ -454,7 +454,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>9.390106424689293e-05</t>
+          <t>0.0003140460466966033</t>
         </is>
       </c>
     </row>
@@ -469,7 +469,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.4950015358626842e-05</t>
+          <t>8.161808364093304e-05</t>
         </is>
       </c>
     </row>

--- a/phys5v48hw/hw6/hw6CPUData.xlsx
+++ b/phys5v48hw/hw6/hw6CPUData.xlsx
@@ -439,7 +439,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.002077734097838402</t>
+          <t>0.0013323070015758276</t>
         </is>
       </c>
     </row>
@@ -454,7 +454,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.0003140460466966033</t>
+          <t>8.897297084331512e-05</t>
         </is>
       </c>
     </row>
@@ -469,7 +469,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>8.161808364093304e-05</t>
+          <t>2.1469080820679665e-05</t>
         </is>
       </c>
     </row>

--- a/phys5v48hw/hw6/hw6CPUData.xlsx
+++ b/phys5v48hw/hw6/hw6CPUData.xlsx
@@ -439,7 +439,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.0013323070015758276</t>
+          <t>0.002695786999538541</t>
         </is>
       </c>
     </row>
@@ -454,7 +454,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>8.897297084331512e-05</t>
+          <t>0.0032033369643613696</t>
         </is>
       </c>
     </row>
@@ -469,7 +469,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.1469080820679665e-05</t>
+          <t>0.0004874500446021557</t>
         </is>
       </c>
     </row>

--- a/phys5v48hw/hw6/hw6CPUData.xlsx
+++ b/phys5v48hw/hw6/hw6CPUData.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,6 +424,11 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>CPU Global Error</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>CPU Time (s)</t>
         </is>
       </c>
@@ -439,7 +444,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.002695786999538541</t>
+          <t>0.0002510975451020525</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0.0009741650428622961</t>
         </is>
       </c>
     </row>
@@ -449,12 +459,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>RK4</t>
+          <t>RK2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.0032033369643613696</t>
+          <t>6.130220242739348e-05</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>5.278701428323984e-05</t>
         </is>
       </c>
     </row>
@@ -464,12 +479,377 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>RK2</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1.5145879413813734e-05</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>5.530205089598894e-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>RK2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>3.7642782991786916e-06</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0.00010420207399874926</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>RK2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>9.383121931660909e-07</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0.00023486802820116282</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>RK2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2.342344066486035e-07</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>0.00040271796751767397</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>RK2</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>5.851570950010654e-08</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>0.0008300059707835317</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>RK4</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>4.928112851132482e-08</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>4.1048042476177216e-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>RK4</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3.0008087681387963e-09</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>5.36659499630332e-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>RK4</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1.8512297250694587e-10</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>0.0001003119396045804</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>RK4</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1.1495138174666408e-11</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>0.00020343600772321224</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>RK4</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>7.168154958492323e-13</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>0.00039165199268609285</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>RK4</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>4.3520742565306136e-14</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0.0008289871038869023</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>RK4</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2.7755575615628914e-15</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>0.00151075201574713</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
           <t>Forward Euler</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>0.0004874500446021557</t>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0.01180531071964952</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>7.112976163625717e-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Forward Euler</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0.005824151915125697</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>9.158044122159481e-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Forward Euler</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0.002892916927534961</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2.5412999093532562e-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Forward Euler</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0.001441725249405168</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2.9842020012438297e-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Forward Euler</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>0.0007196862799060955</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>5.759298801422119e-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Forward Euler</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>0.0003595499169070093</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>0.00011652300599962473</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Forward Euler</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>0.00017970176017118034</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>0.00022662896662950516</t>
         </is>
       </c>
     </row>

--- a/phys5v48hw/hw6/hw6CPUData.xlsx
+++ b/phys5v48hw/hw6/hw6CPUData.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,10 +424,15 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>CPU Global Error</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>CPU Time (s)</t>
         </is>
@@ -444,12 +449,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>0.0002510975451020525</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>0.0009741650428622961</t>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.0016800770536065102</t>
         </is>
       </c>
     </row>
@@ -464,12 +474,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>6.130220242739348e-05</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>5.278701428323984e-05</t>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.00011545699089765549</t>
         </is>
       </c>
     </row>
@@ -484,12 +499,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>1.5145879413813734e-05</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>5.530205089598894e-05</t>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0.00018007808830589056</t>
         </is>
       </c>
     </row>
@@ -504,12 +524,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>3.7642782991786916e-06</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>0.00010420207399874926</t>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0.00024861504789441824</t>
         </is>
       </c>
     </row>
@@ -524,12 +549,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>9.383121931660909e-07</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>0.00023486802820116282</t>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.00020550203043967485</t>
         </is>
       </c>
     </row>
@@ -544,12 +574,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>2.342344066486035e-07</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>0.00040271796751767397</t>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0.00041062699165195227</t>
         </is>
       </c>
     </row>
@@ -564,12 +599,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
           <t>5.851570950010654e-08</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>0.0008300059707835317</t>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0.0008477340452373028</t>
         </is>
       </c>
     </row>
@@ -584,12 +624,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
           <t>4.928112851132482e-08</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>4.1048042476177216e-05</t>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>3.9637903682887554e-05</t>
         </is>
       </c>
     </row>
@@ -604,12 +649,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
           <t>3.0008087681387963e-09</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>5.36659499630332e-05</t>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>6.669305730611086e-05</t>
         </is>
       </c>
     </row>
@@ -624,12 +674,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
           <t>1.8512297250694587e-10</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>0.0001003119396045804</t>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0.0001060430658981204</t>
         </is>
       </c>
     </row>
@@ -644,12 +699,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
           <t>1.1495138174666408e-11</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>0.00020343600772321224</t>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0.00021100288722664118</t>
         </is>
       </c>
     </row>
@@ -664,12 +724,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
           <t>7.168154958492323e-13</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>0.00039165199268609285</t>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0.0003994130529463291</t>
         </is>
       </c>
     </row>
@@ -684,12 +749,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
           <t>4.3520742565306136e-14</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>0.0008289871038869023</t>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0.0007895319722592831</t>
         </is>
       </c>
     </row>
@@ -704,12 +774,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
           <t>2.7755575615628914e-15</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>0.00151075201574713</t>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0.0015179890906438231</t>
         </is>
       </c>
     </row>
@@ -724,12 +799,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
           <t>0.01180531071964952</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>7.112976163625717e-06</t>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>7.363967597484589e-06</t>
         </is>
       </c>
     </row>
@@ -744,12 +824,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
           <t>0.005824151915125697</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>9.158044122159481e-06</t>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>9.777024388313293e-06</t>
         </is>
       </c>
     </row>
@@ -764,12 +849,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
           <t>0.002892916927534961</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2.5412999093532562e-05</t>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>1.6813981346786022e-05</t>
         </is>
       </c>
     </row>
@@ -784,12 +874,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
           <t>0.001441725249405168</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2.9842020012438297e-05</t>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2.9643066227436066e-05</t>
         </is>
       </c>
     </row>
@@ -804,12 +899,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
           <t>0.0007196862799060955</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>5.759298801422119e-05</t>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>5.7230936363339424e-05</t>
         </is>
       </c>
     </row>
@@ -824,12 +924,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
           <t>0.0003595499169070093</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>0.00011652300599962473</t>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0.00011583301238715649</t>
         </is>
       </c>
     </row>
@@ -844,12 +949,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
           <t>0.00017970176017118034</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>0.00022662896662950516</t>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0.00022878206800669432</t>
         </is>
       </c>
     </row>

--- a/phys5v48hw/hw6/hw6CPUData.xlsx
+++ b/phys5v48hw/hw6/hw6CPUData.xlsx
@@ -459,7 +459,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.0016800770536065102</t>
+          <t>0.0017476329812780023</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.00011545699089765549</t>
+          <t>4.18039271607995e-05</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.00018007808830589056</t>
+          <t>5.343393422663212e-05</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.00024861504789441824</t>
+          <t>0.0001236980315297842</t>
         </is>
       </c>
     </row>
@@ -559,7 +559,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.00020550203043967485</t>
+          <t>0.0002081680577248335</t>
         </is>
       </c>
     </row>
@@ -584,7 +584,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.00041062699165195227</t>
+          <t>0.0004222859861329198</t>
         </is>
       </c>
     </row>
@@ -609,7 +609,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.0008477340452373028</t>
+          <t>0.0008776040049269795</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>3.9637903682887554e-05</t>
+          <t>4.1328021325170994e-05</t>
         </is>
       </c>
     </row>
@@ -659,7 +659,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>6.669305730611086e-05</t>
+          <t>5.36179868504405e-05</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.0001060430658981204</t>
+          <t>0.00010937405750155449</t>
         </is>
       </c>
     </row>
@@ -709,7 +709,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.00021100288722664118</t>
+          <t>0.0002162150340154767</t>
         </is>
       </c>
     </row>
@@ -734,7 +734,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.0003994130529463291</t>
+          <t>0.00039151497185230255</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.0007895319722592831</t>
+          <t>0.0008612739620730281</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.0015179890906438231</t>
+          <t>0.001483372994698584</t>
         </is>
       </c>
     </row>
@@ -809,7 +809,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>7.363967597484589e-06</t>
+          <t>6.8320659920573235e-06</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>9.777024388313293e-06</t>
+          <t>8.904957212507725e-06</t>
         </is>
       </c>
     </row>
@@ -859,7 +859,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.6813981346786022e-05</t>
+          <t>2.505793236196041e-05</t>
         </is>
       </c>
     </row>
@@ -884,7 +884,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2.9643066227436066e-05</t>
+          <t>2.8913957066833973e-05</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>5.7230936363339424e-05</t>
+          <t>5.573895759880543e-05</t>
         </is>
       </c>
     </row>
@@ -934,7 +934,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.00011583301238715649</t>
+          <t>0.0001129519660025835</t>
         </is>
       </c>
     </row>
@@ -959,7 +959,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.00022878206800669432</t>
+          <t>0.0002433129120618105</t>
         </is>
       </c>
     </row>

--- a/phys5v48hw/hw6/hw6CPUData.xlsx
+++ b/phys5v48hw/hw6/hw6CPUData.xlsx
@@ -459,7 +459,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.0017476329812780023</t>
+          <t>0.007855943986214697</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>4.18039271607995e-05</t>
+          <t>0.00011186697520315647</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>5.343393422663212e-05</t>
+          <t>0.0001868540421128273</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.0001236980315297842</t>
+          <t>0.00023472902830690145</t>
         </is>
       </c>
     </row>
@@ -559,7 +559,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.0002081680577248335</t>
+          <t>0.00020274205598980188</t>
         </is>
       </c>
     </row>
@@ -584,7 +584,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.0004222859861329198</t>
+          <t>0.00045865902211517096</t>
         </is>
       </c>
     </row>
@@ -609,7 +609,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.0008776040049269795</t>
+          <t>0.0008729220135137439</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>4.1328021325170994e-05</t>
+          <t>4.261499270796776e-05</t>
         </is>
       </c>
     </row>
@@ -659,7 +659,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>5.36179868504405e-05</t>
+          <t>5.4212985560297966e-05</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.00010937405750155449</t>
+          <t>0.00010280800051987171</t>
         </is>
       </c>
     </row>
@@ -709,7 +709,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.0002162150340154767</t>
+          <t>0.0002008459996432066</t>
         </is>
       </c>
     </row>
@@ -734,7 +734,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.00039151497185230255</t>
+          <t>0.0004288539057597518</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.0008612739620730281</t>
+          <t>0.0007841599872335792</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.001483372994698584</t>
+          <t>0.0015812619822099805</t>
         </is>
       </c>
     </row>
@@ -809,7 +809,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>6.8320659920573235e-06</t>
+          <t>7.255002856254578e-06</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>8.904957212507725e-06</t>
+          <t>9.6180010586977e-06</t>
         </is>
       </c>
     </row>
@@ -859,7 +859,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2.505793236196041e-05</t>
+          <t>2.7009984478354454e-05</t>
         </is>
       </c>
     </row>
@@ -884,7 +884,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2.8913957066833973e-05</t>
+          <t>2.965691965073347e-05</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>5.573895759880543e-05</t>
+          <t>5.6898919865489006e-05</t>
         </is>
       </c>
     </row>
@@ -934,7 +934,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.0001129519660025835</t>
+          <t>0.00011393206659704447</t>
         </is>
       </c>
     </row>
@@ -959,7 +959,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.0002433129120618105</t>
+          <t>0.0002476009540259838</t>
         </is>
       </c>
     </row>

--- a/phys5v48hw/hw6/hw6CPUData.xlsx
+++ b/phys5v48hw/hw6/hw6CPUData.xlsx
@@ -459,7 +459,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.007855943986214697</t>
+          <t>0.0007071320433169603</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.00011186697520315647</t>
+          <t>1.855392474681139e-05</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.0001868540421128273</t>
+          <t>2.9875081963837147e-05</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.00023472902830690145</t>
+          <t>5.573593080043793e-05</t>
         </is>
       </c>
     </row>
@@ -559,7 +559,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.00020274205598980188</t>
+          <t>0.00010907906107604504</t>
         </is>
       </c>
     </row>
@@ -584,7 +584,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.00045865902211517096</t>
+          <t>0.00020478898659348488</t>
         </is>
       </c>
     </row>
@@ -609,7 +609,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.0008729220135137439</t>
+          <t>0.0004097600467503071</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>4.261499270796776e-05</t>
+          <t>1.9647064618766308e-05</t>
         </is>
       </c>
     </row>
@@ -659,7 +659,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>5.4212985560297966e-05</t>
+          <t>2.8335023671388626e-05</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.00010280800051987171</t>
+          <t>5.102704744786024e-05</t>
         </is>
       </c>
     </row>
@@ -709,7 +709,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.0002008459996432066</t>
+          <t>0.00010490696877241135</t>
         </is>
       </c>
     </row>
@@ -734,7 +734,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.0004288539057597518</t>
+          <t>0.0002001700922846794</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.0007841599872335792</t>
+          <t>0.0003994150320068002</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.0015812619822099805</t>
+          <t>0.0008075919467955828</t>
         </is>
       </c>
     </row>
@@ -809,7 +809,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>7.255002856254578e-06</t>
+          <t>4.3030595406889915e-06</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>9.6180010586977e-06</t>
+          <t>5.034962669014931e-06</t>
         </is>
       </c>
     </row>
@@ -859,7 +859,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2.7009984478354454e-05</t>
+          <t>7.925904355943203e-06</t>
         </is>
       </c>
     </row>
@@ -884,7 +884,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2.965691965073347e-05</t>
+          <t>1.4335964806377888e-05</t>
         </is>
       </c>
     </row>
@@ -909,7 +909,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>5.6898919865489006e-05</t>
+          <t>2.7777045033872128e-05</t>
         </is>
       </c>
     </row>
@@ -934,7 +934,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.00011393206659704447</t>
+          <t>5.8227917179465294e-05</t>
         </is>
       </c>
     </row>
@@ -959,7 +959,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.0002476009540259838</t>
+          <t>0.00011131295468658209</t>
         </is>
       </c>
     </row>
